--- a/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,78</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>21,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,75</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>14,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,68; 16,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,65; 21,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,9; 30,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,45; 9,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,36; 11,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,89; 13,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,7; 12,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,8; 15,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,48; 19,98</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,63; 48,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,58; 63,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,75; 88,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,81; 11,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,4; 14,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,21; 17,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,96; 21,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,77; 26,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,59; 35,02</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,43</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,75</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>20,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,38; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,73; 16,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,62; 41,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,81; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,1; 7,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,61; 12,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,2; 4,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,28; 9,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,17; 25,28</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-1,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,68; 17,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,69; 46,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65,81; 120,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,62; 5,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,47; 8,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,15; 15,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,58; 8,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,24; 16,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,55; 43,05</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,55</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>48,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,76</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>26,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,28; 21,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,39; 37,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,7; 54,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,97; 6,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,8; 12,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,57; 11,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,47; 12,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,21; 23,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,66; 31,23</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>107,07%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>169,09%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,71; 87,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,77; 151,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>123,7; 232,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,81; 7,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,11; 15,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,9; 14,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,47; 22,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,09; 43,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,17; 58,51</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,46</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>21,37</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,69</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,86</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>23,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,2; 25,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,71; 28,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,09; 42,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,45; 6,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,01; 5,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,35; 14,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,36; 14,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,28; 15,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,72; 30,02</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>114,42%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,69; 96,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,29; 103,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,28; 156,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,14; 7,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,85; 7,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,09; 17,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,13; 26,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,02; 28,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,59; 54,66</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-5,7</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>21,37</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>52,04</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,47</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,9</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-5,93</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,92</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,49; 4,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,14; 30,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,34; 60,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,23; 0,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,72; 12,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,78; 15,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,11; 0,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,9; 19,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,7; 36,8</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-15,8%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>144,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-7,42%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-9,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-36,22; 15,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,92; 99,87</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>105,98; 206,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,69; 0,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,79; 15,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,36; 19,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,29; 0,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,32; 34,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,02; 64,26</t>
         </is>
       </c>
     </row>
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>16,63</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,22</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>50,18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,79</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>26,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,51; 24,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,7; 25,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,42; 56,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,84; 4,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,07; 6,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,04; 8,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,51; 13,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,02; 14,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,97; 31,98</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>187,18%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-1,45%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,55; 108,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,02; 111,09</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>136,45; 256,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,58; 5,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,74; 8,25</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,01; 10,68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,47; 24,69</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,17; 27,55</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,88; 60,03</t>
         </is>
       </c>
     </row>
@@ -1920,47 +1920,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,66</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>31,69</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-3,95</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,93</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,56; 11,23</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,95; 17,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,6; 38,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,86; 0,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,38; 4,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,58; 10,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,48; 4,39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,58; 10,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,41; 26,7</t>
         </is>
       </c>
     </row>
@@ -2026,47 +2026,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,57%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,55; 29,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,47; 46,26</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,64; 102,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,9; 0,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,83; 4,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,66; 12,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,23; 7,1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,9; 17,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,92; 41,95</t>
         </is>
       </c>
     </row>
@@ -2136,47 +2136,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>27,15</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,16</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,21</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>16,07</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,35</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,01; 20,66</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,37; 32,52</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,88; 14,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,06; 4,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,16; 9,46</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,11; 14,57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,16; 11,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,81; 19,47</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,96; 12,99</t>
         </is>
       </c>
     </row>
@@ -2242,47 +2242,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,32; 74,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65,42; 114,37</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-49,68; 46,73</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,66; 6,17</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,6; 11,98</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,74; 18,34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,85; 20,88</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,59; 35,66</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,64; 23,27</t>
         </is>
       </c>
     </row>
@@ -2352,47 +2352,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,92</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>27,11</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,13</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,99; 11,99</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,18; 21,09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,96; 32,59</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,25; 1,38</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,64; 5,1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,81; 9,37</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,73; 6,16</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,59; 12,75</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,8; 20,9</t>
         </is>
       </c>
     </row>
@@ -2458,47 +2458,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,64%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,42; 36,42</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,58; 64,3</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,95; 97,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,65; 1,67</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,93; 6,15</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,81; 11,19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,55; 10,5</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,77; 21,72</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,69; 35,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,51</t>
+          <t>19,16</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>8,19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,69</t>
+          <t>14,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 16,29</t>
+          <t>-0,84; 16,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 21,37</t>
+          <t>4,35; 21,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 30,13</t>
+          <t>10,84; 27,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 9,5</t>
+          <t>-2,59; 10,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 11,41</t>
+          <t>-0,27; 11,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 13,57</t>
+          <t>2,42; 13,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 12,31</t>
+          <t>0,33; 11,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 15,29</t>
+          <t>4,07; 15,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,48; 19,98</t>
+          <t>8,55; 19,51</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 48,14</t>
+          <t>-2,07; 47,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 63,18</t>
+          <t>9,99; 63,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,75; 88,58</t>
+          <t>25,17; 81,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 11,93</t>
+          <t>-2,95; 12,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 14,29</t>
+          <t>-0,31; 14,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 17,18</t>
+          <t>2,74; 17,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 21,04</t>
+          <t>0,51; 20,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 26,36</t>
+          <t>6,46; 26,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,59; 35,02</t>
+          <t>13,23; 34,89</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34,43</t>
+          <t>35,19</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,75</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20,81</t>
+          <t>21,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 5,99</t>
+          <t>-7,04; 5,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 16,05</t>
+          <t>3,14; 14,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,62; 41,48</t>
+          <t>27,91; 41,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 4,58</t>
+          <t>-4,53; 4,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 7,17</t>
+          <t>-2,41; 7,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 12,24</t>
+          <t>2,91; 11,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 4,71</t>
+          <t>-4,64; 4,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 9,89</t>
+          <t>1,67; 10,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 25,28</t>
+          <t>17,15; 25,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 17,62</t>
+          <t>-17,28; 16,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 46,16</t>
+          <t>7,58; 42,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,81; 120,82</t>
+          <t>67,97; 121,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 5,61</t>
+          <t>-5,31; 5,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 8,82</t>
+          <t>-2,75; 8,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 15,12</t>
+          <t>3,51; 14,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 8,04</t>
+          <t>-7,34; 7,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 16,84</t>
+          <t>2,64; 16,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,55; 43,05</t>
+          <t>27,26; 42,87</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48,24</t>
+          <t>47,66</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26,91</t>
+          <t>26,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 21,21</t>
+          <t>5,92; 20,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,39; 37,67</t>
+          <t>23,41; 38,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,7; 54,83</t>
+          <t>40,44; 54,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 6,21</t>
+          <t>-4,65; 6,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 12,04</t>
+          <t>1,59; 11,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,29</t>
+          <t>1,54; 11,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,3</t>
+          <t>0,97; 12,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,21; 23,34</t>
+          <t>13,27; 23,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,66; 31,23</t>
+          <t>21,88; 31,42</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169,09%</t>
+          <t>167,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,71; 87,55</t>
+          <t>18,88; 83,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68,77; 151,52</t>
+          <t>71,08; 154,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123,7; 232,97</t>
+          <t>120,83; 226,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 7,67</t>
+          <t>-5,49; 8,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 15,04</t>
+          <t>1,89; 14,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 14,3</t>
+          <t>1,86; 14,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 22,81</t>
+          <t>1,74; 23,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,09; 43,39</t>
+          <t>21,89; 44,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,17; 58,51</t>
+          <t>35,99; 58,76</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34,65</t>
+          <t>34,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23,57</t>
+          <t>20,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,2; 25,55</t>
+          <t>11,45; 25,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,71; 28,52</t>
+          <t>14,44; 29,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,09; 42,59</t>
+          <t>24,81; 42,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 6,23</t>
+          <t>-4,57; 6,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 5,98</t>
+          <t>-5,89; 5,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,15</t>
+          <t>0,36; 11,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 14,56</t>
+          <t>4,53; 14,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 15,5</t>
+          <t>6,0; 15,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,72; 30,02</t>
+          <t>14,94; 25,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114,42%</t>
+          <t>113,22%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,69; 96,73</t>
+          <t>33,76; 99,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39,29; 103,93</t>
+          <t>41,91; 111,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,28; 156,13</t>
+          <t>72,08; 161,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 7,83</t>
+          <t>-5,39; 8,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 7,55</t>
+          <t>-6,9; 7,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 17,96</t>
+          <t>0,57; 14,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,13; 26,86</t>
+          <t>7,81; 26,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,02; 28,44</t>
+          <t>10,08; 28,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,59; 54,66</t>
+          <t>25,21; 46,86</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52,04</t>
+          <t>52,09</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30,89</t>
+          <t>29,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 4,99</t>
+          <t>-14,34; 4,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,14; 30,57</t>
+          <t>11,96; 30,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44,34; 60,44</t>
+          <t>43,93; 59,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 0,5</t>
+          <t>-13,11; 0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 12,46</t>
+          <t>1,2; 12,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,78; 15,35</t>
+          <t>2,46; 13,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 0,5</t>
+          <t>-12,37; 1,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,9; 19,77</t>
+          <t>7,55; 20,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,7; 36,8</t>
+          <t>25,0; 35,22</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144,25%</t>
+          <t>144,38%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 15,49</t>
+          <t>-35,66; 14,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>26,92; 99,87</t>
+          <t>27,85; 100,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105,98; 206,12</t>
+          <t>103,45; 197,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 0,62</t>
+          <t>-14,98; 0,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,79; 15,37</t>
+          <t>1,34; 14,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,36; 19,1</t>
+          <t>2,72; 15,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 0,8</t>
+          <t>-19,35; 1,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10,32; 34,16</t>
+          <t>11,5; 35,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>39,02; 64,26</t>
+          <t>38,05; 61,66</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50,18</t>
+          <t>50,55</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26,62</t>
+          <t>26,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,51; 24,51</t>
+          <t>8,8; 24,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8,7; 25,01</t>
+          <t>9,4; 25,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43,42; 56,95</t>
+          <t>43,54; 57,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,4</t>
+          <t>-6,68; 4,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 6,93</t>
+          <t>-5,52; 6,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 8,93</t>
+          <t>-0,27; 9,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,45</t>
+          <t>1,42; 13,48</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,02; 14,78</t>
+          <t>3,19; 14,84</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>21,97; 31,98</t>
+          <t>21,74; 31,94</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>187,18%</t>
+          <t>188,57%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>27,55; 108,52</t>
+          <t>27,48; 106,59</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>29,02; 111,09</t>
+          <t>30,35; 108,47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>136,45; 256,38</t>
+          <t>139,22; 258,2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 5,12</t>
+          <t>-7,47; 5,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 8,25</t>
+          <t>-6,12; 7,31</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 10,68</t>
+          <t>-0,27; 11,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,47; 24,69</t>
+          <t>2,43; 25,25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5,17; 27,55</t>
+          <t>5,22; 28,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>35,88; 60,03</t>
+          <t>35,87; 60,46</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31,69</t>
+          <t>31,81</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18,93</t>
+          <t>16,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 11,23</t>
+          <t>-0,56; 10,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,95; 17,22</t>
+          <t>6,16; 17,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25,6; 38,08</t>
+          <t>25,64; 37,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 0,55</t>
+          <t>-7,86; 0,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,06</t>
+          <t>-3,4; 4,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 10,71</t>
+          <t>-2,82; 4,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,39</t>
+          <t>-3,56; 4,39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,44</t>
+          <t>2,44; 9,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,41; 26,7</t>
+          <t>12,48; 19,98</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 29,45</t>
+          <t>-1,37; 28,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,47; 46,26</t>
+          <t>13,94; 45,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58,64; 102,51</t>
+          <t>58,3; 97,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 0,67</t>
+          <t>-8,91; 0,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,82</t>
+          <t>-3,86; 5,16</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 12,78</t>
+          <t>-3,16; 5,75</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 7,1</t>
+          <t>-5,41; 7,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,9; 17,0</t>
+          <t>3,71; 15,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>21,92; 41,95</t>
+          <t>19,19; 32,49</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>12,24</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,16</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>11,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10,01; 20,66</t>
+          <t>10,45; 20,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>22,37; 32,52</t>
+          <t>21,96; 32,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 14,02</t>
+          <t>7,31; 17,68</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 4,94</t>
+          <t>-2,83; 4,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,16; 9,46</t>
+          <t>1,5; 8,8</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,57</t>
+          <t>7,66; 14,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,61</t>
+          <t>4,81; 11,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>12,81; 19,47</t>
+          <t>12,79; 19,66</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 12,99</t>
+          <t>8,02; 14,84</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>30,32; 74,82</t>
+          <t>31,32; 72,74</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>65,42; 114,37</t>
+          <t>64,74; 113,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 46,73</t>
+          <t>21,89; 62,16</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 6,17</t>
+          <t>-3,47; 5,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,98</t>
+          <t>1,77; 11,03</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,74; 18,34</t>
+          <t>9,17; 18,18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,85; 20,88</t>
+          <t>8,02; 21,26</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>21,59; 35,66</t>
+          <t>21,62; 35,69</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 23,27</t>
+          <t>13,58; 27,24</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>27,11</t>
+          <t>31,28</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,48</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>17,45</t>
+          <t>18,9</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,99</t>
+          <t>6,86; 11,81</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>16,18; 21,09</t>
+          <t>16,48; 21,23</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11,96; 32,59</t>
+          <t>28,77; 33,56</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,38</t>
+          <t>-2,22; 1,43</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,1</t>
+          <t>1,57; 4,96</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,37</t>
+          <t>4,99; 8,16</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,16</t>
+          <t>2,91; 6,23</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,59; 12,75</t>
+          <t>9,43; 12,76</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8,8; 20,9</t>
+          <t>17,31; 20,54</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>19,42; 36,42</t>
+          <t>19,42; 35,92</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>45,58; 64,3</t>
+          <t>46,31; 64,22</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>35,95; 97,21</t>
+          <t>80,67; 101,88</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,67</t>
+          <t>-2,63; 1,71</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,15</t>
+          <t>1,85; 5,96</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,19</t>
+          <t>5,86; 9,83</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,5</t>
+          <t>4,79; 10,62</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15,77; 21,72</t>
+          <t>15,58; 21,74</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>14,69; 35,4</t>
+          <t>28,61; 35,25</t>
         </is>
       </c>
     </row>
